--- a/Result/profitability/1503.xlsx
+++ b/Result/profitability/1503.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.47</v>
       </c>
       <c r="M2" t="n">
-        <v>1.46625</v>
+        <v>1.57875</v>
       </c>
       <c r="N2" t="n">
-        <v>20.905</v>
+        <v>20.81125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.44</v>
       </c>
       <c r="M3" t="n">
-        <v>1.3525</v>
+        <v>1.52875</v>
       </c>
       <c r="N3" t="n">
-        <v>20.15375</v>
+        <v>20.6675</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,16 +899,16 @@
         <v>0.46</v>
       </c>
       <c r="M4" t="n">
-        <v>1.305</v>
+        <v>1.2925</v>
       </c>
       <c r="N4" t="n">
-        <v>20.15625</v>
+        <v>19.9825</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.15</v>
       </c>
       <c r="M5" t="n">
-        <v>1.03</v>
+        <v>1.0975</v>
       </c>
       <c r="N5" t="n">
-        <v>18.96625</v>
+        <v>18.88</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.39</v>
       </c>
       <c r="M6" t="n">
-        <v>0.865</v>
+        <v>0.97</v>
       </c>
       <c r="N6" t="n">
-        <v>18.29875</v>
+        <v>18.595</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>5.05</v>
       </c>
       <c r="M7" t="n">
-        <v>1.32</v>
+        <v>1.5</v>
       </c>
       <c r="N7" t="n">
-        <v>20.53875</v>
+        <v>21.16</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.58</v>
       </c>
       <c r="M8" t="n">
-        <v>1.29125</v>
+        <v>1.22375</v>
       </c>
       <c r="N8" t="n">
-        <v>20.98</v>
+        <v>20.78</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1503</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>9563</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7443</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2120</v>
+      </c>
+      <c r="F75" t="n">
+        <v>22.17</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1269</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>166</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1435</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1171</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.68875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.2925</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1935483870967742</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.599999999999998</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.0673117374842237</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3157894736842106</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.6899999999999977</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.03018372703412064</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
